--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0002.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0002.xlsx
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
